--- a/formlar/16. Organik Üretim/EMS.OR.FRM.21.18. Organik Final Kontrol ve Ürün Onay Formu.xlsx
+++ b/formlar/16. Organik Üretim/EMS.OR.FRM.21.18. Organik Final Kontrol ve Ürün Onay Formu.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,12 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -89,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -166,11 +172,94 @@
       <left style="medium"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -246,6 +335,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -350,6 +491,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -380,6 +524,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -705,31 +852,32 @@
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC FINAL INSPECTION AND PRODUCT APPROVAL FORM
+      <c r="D1" s="45" t="inlineStr">
+        <is>
+          <t>ORGANİK FİNAL KONTROL VE ÜRÜN ONAY FORMU
+ORGANIC FINAL INSPECTION AND PRODUCT APPROVAL FORM
 نموذج الفحص النهائي واعتماد المنتج العضوي</t>
         </is>
       </c>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="4" t="n"/>
-      <c r="O1" s="5" t="n"/>
+      <c r="E1" s="46" t="n"/>
+      <c r="F1" s="46" t="n"/>
+      <c r="G1" s="46" t="n"/>
+      <c r="H1" s="46" t="n"/>
+      <c r="I1" s="46" t="n"/>
+      <c r="J1" s="46" t="n"/>
+      <c r="K1" s="46" t="n"/>
+      <c r="L1" s="46" t="n"/>
+      <c r="M1" s="46" t="n"/>
+      <c r="N1" s="46" t="n"/>
+      <c r="O1" s="47" t="n"/>
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="6" t="inlineStr">
+      <c r="R1" s="48" t="inlineStr">
         <is>
           <t>DATE / التاريخ</t>
         </is>
       </c>
-      <c r="S1" s="7" t="n"/>
+      <c r="S1" s="49" t="n"/>
       <c r="T1" s="8" t="inlineStr">
         <is>
           <t>….../….../.…</t>
@@ -740,26 +888,16 @@
       <c r="A2" s="9" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="12" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="O2" s="51" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="48" t="inlineStr">
         <is>
           <t>FORM NUMBER / رقم النموذج</t>
         </is>
       </c>
-      <c r="S2" s="7" t="n"/>
+      <c r="S2" s="49" t="n"/>
       <c r="T2" s="13" t="inlineStr">
         <is>
           <t>EMS.OR.FRM.21.18</t>
@@ -770,26 +908,16 @@
       <c r="A3" s="9" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="11" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="12" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="O3" s="51" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="48" t="inlineStr">
         <is>
           <t>REVISION / المراجعة</t>
         </is>
       </c>
-      <c r="S3" s="7" t="n"/>
+      <c r="S3" s="49" t="n"/>
       <c r="T3" s="8" t="inlineStr">
         <is>
           <t>R00</t>
@@ -800,26 +928,26 @@
       <c r="A4" s="9" t="n"/>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="n"/>
-      <c r="J4" s="15" t="n"/>
-      <c r="K4" s="15" t="n"/>
-      <c r="L4" s="15" t="n"/>
-      <c r="M4" s="15" t="n"/>
-      <c r="N4" s="15" t="n"/>
-      <c r="O4" s="16" t="n"/>
+      <c r="D4" s="52" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="53" t="n"/>
+      <c r="L4" s="53" t="n"/>
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n"/>
+      <c r="O4" s="54" t="n"/>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="48" t="inlineStr">
         <is>
           <t>PUBLIC. DATE / تاريخ النشر</t>
         </is>
       </c>
-      <c r="S4" s="7" t="n"/>
+      <c r="S4" s="49" t="n"/>
       <c r="T4" s="8" t="inlineStr">
         <is>
           <t>22.10.2026</t>
@@ -827,746 +955,732 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>GENERAL INFORMATION / المعلومات العامة</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="18" t="n"/>
-      <c r="I6" s="18" t="n"/>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="18" t="n"/>
-      <c r="O6" s="18" t="n"/>
-      <c r="P6" s="18" t="n"/>
-      <c r="Q6" s="18" t="n"/>
-      <c r="R6" s="18" t="n"/>
-      <c r="S6" s="18" t="n"/>
-      <c r="T6" s="7" t="n"/>
+      <c r="B6" s="56" t="n"/>
+      <c r="C6" s="56" t="n"/>
+      <c r="D6" s="56" t="n"/>
+      <c r="E6" s="56" t="n"/>
+      <c r="F6" s="56" t="n"/>
+      <c r="G6" s="56" t="n"/>
+      <c r="H6" s="56" t="n"/>
+      <c r="I6" s="56" t="n"/>
+      <c r="J6" s="56" t="n"/>
+      <c r="K6" s="56" t="n"/>
+      <c r="L6" s="56" t="n"/>
+      <c r="M6" s="56" t="n"/>
+      <c r="N6" s="56" t="n"/>
+      <c r="O6" s="56" t="n"/>
+      <c r="P6" s="56" t="n"/>
+      <c r="Q6" s="56" t="n"/>
+      <c r="R6" s="56" t="n"/>
+      <c r="S6" s="56" t="n"/>
+      <c r="T6" s="49" t="n"/>
     </row>
     <row r="7" ht="34.05" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>Date
 التاريخ</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="B7" s="56" t="n"/>
+      <c r="C7" s="56" t="n"/>
+      <c r="D7" s="56" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>Order / PO No
 رقم الطلب</t>
         </is>
       </c>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="G7" s="56" t="n"/>
+      <c r="H7" s="56" t="n"/>
+      <c r="I7" s="56" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="58" t="inlineStr">
         <is>
           <t>Customer
 العميل</t>
         </is>
       </c>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="21" t="n"/>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="L7" s="56" t="n"/>
+      <c r="M7" s="56" t="n"/>
+      <c r="N7" s="56" t="n"/>
+      <c r="O7" s="49" t="n"/>
+      <c r="P7" s="58" t="inlineStr">
         <is>
           <t>Style No
 رقم الموديل</t>
         </is>
       </c>
-      <c r="Q7" s="20" t="n"/>
-      <c r="R7" s="20" t="n"/>
-      <c r="S7" s="20" t="n"/>
-      <c r="T7" s="21" t="n"/>
+      <c r="Q7" s="56" t="n"/>
+      <c r="R7" s="56" t="n"/>
+      <c r="S7" s="56" t="n"/>
+      <c r="T7" s="49" t="n"/>
     </row>
     <row r="8" ht="34.05" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="57" t="inlineStr">
         <is>
           <t>Organic Lot No
 رقم الدفعة العضوية</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="B8" s="56" t="n"/>
+      <c r="C8" s="56" t="n"/>
+      <c r="D8" s="56" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="58" t="inlineStr">
         <is>
           <t>Carton Qty
 عدد الكراتين</t>
         </is>
       </c>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="G8" s="56" t="n"/>
+      <c r="H8" s="56" t="n"/>
+      <c r="I8" s="56" t="n"/>
+      <c r="J8" s="49" t="n"/>
+      <c r="K8" s="58" t="inlineStr">
         <is>
           <t>Prepared by
 المعد</t>
         </is>
       </c>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="21" t="n"/>
-      <c r="P8" s="22" t="inlineStr">
+      <c r="L8" s="56" t="n"/>
+      <c r="M8" s="56" t="n"/>
+      <c r="N8" s="56" t="n"/>
+      <c r="O8" s="49" t="n"/>
+      <c r="P8" s="58" t="inlineStr">
         <is>
           <t>Standard ☐ GOTS ☐ OCS
 المعيار</t>
         </is>
       </c>
-      <c r="Q8" s="20" t="n"/>
-      <c r="R8" s="20" t="n"/>
-      <c r="S8" s="20" t="n"/>
-      <c r="T8" s="21" t="n"/>
+      <c r="Q8" s="56" t="n"/>
+      <c r="R8" s="56" t="n"/>
+      <c r="S8" s="56" t="n"/>
+      <c r="T8" s="49" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t>FINAL INSPECTION AND APPROVAL / الفحص النهائي والاعتماد</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="n"/>
-      <c r="I10" s="18" t="n"/>
-      <c r="J10" s="18" t="n"/>
-      <c r="K10" s="18" t="n"/>
-      <c r="L10" s="18" t="n"/>
-      <c r="M10" s="18" t="n"/>
-      <c r="N10" s="18" t="n"/>
-      <c r="O10" s="18" t="n"/>
-      <c r="P10" s="18" t="n"/>
-      <c r="Q10" s="18" t="n"/>
-      <c r="R10" s="18" t="n"/>
-      <c r="S10" s="18" t="n"/>
-      <c r="T10" s="7" t="n"/>
+      <c r="B10" s="56" t="n"/>
+      <c r="C10" s="56" t="n"/>
+      <c r="D10" s="56" t="n"/>
+      <c r="E10" s="56" t="n"/>
+      <c r="F10" s="56" t="n"/>
+      <c r="G10" s="56" t="n"/>
+      <c r="H10" s="56" t="n"/>
+      <c r="I10" s="56" t="n"/>
+      <c r="J10" s="56" t="n"/>
+      <c r="K10" s="56" t="n"/>
+      <c r="L10" s="56" t="n"/>
+      <c r="M10" s="56" t="n"/>
+      <c r="N10" s="56" t="n"/>
+      <c r="O10" s="56" t="n"/>
+      <c r="P10" s="56" t="n"/>
+      <c r="Q10" s="56" t="n"/>
+      <c r="R10" s="56" t="n"/>
+      <c r="S10" s="56" t="n"/>
+      <c r="T10" s="49" t="n"/>
     </row>
     <row r="11" ht="37.2" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="B11" s="49" t="n"/>
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Carton / Lot No
 رقم الكرتونة / الدفعة</t>
         </is>
       </c>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="D11" s="56" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>Sample Size
 حجم العينة</t>
         </is>
       </c>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="60" t="inlineStr">
         <is>
           <t>Defects Found
 العيوب</t>
         </is>
       </c>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="24" t="inlineStr">
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="60" t="inlineStr">
         <is>
           <t>Composition Label OK
 ملصق التركيب سليم</t>
         </is>
       </c>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="K11" s="49" t="n"/>
+      <c r="L11" s="60" t="inlineStr">
         <is>
           <t>Organic Claim / Logo OK
 الادعاء العضوي / الشعار سليم</t>
         </is>
       </c>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="M11" s="56" t="n"/>
+      <c r="N11" s="49" t="n"/>
+      <c r="O11" s="60" t="inlineStr">
         <is>
           <t>Result (Pass / Fail)
 النتيجة</t>
         </is>
       </c>
-      <c r="P11" s="21" t="n"/>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="P11" s="49" t="n"/>
+      <c r="Q11" s="60" t="inlineStr">
         <is>
           <t>Inspector
 المفتش</t>
         </is>
       </c>
-      <c r="R11" s="21" t="n"/>
-      <c r="S11" s="24" t="inlineStr">
+      <c r="R11" s="49" t="n"/>
+      <c r="S11" s="60" t="inlineStr">
         <is>
           <t>Remarks
 ملاحظات</t>
         </is>
       </c>
-      <c r="T11" s="21" t="n"/>
+      <c r="T11" s="49" t="n"/>
     </row>
     <row r="12" ht="22.05" customHeight="1">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="27" t="n"/>
-      <c r="M12" s="28" t="n"/>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="27" t="n"/>
-      <c r="P12" s="26" t="n"/>
-      <c r="Q12" s="27" t="n"/>
-      <c r="R12" s="26" t="n"/>
-      <c r="S12" s="27" t="n"/>
-      <c r="T12" s="26" t="n"/>
+      <c r="B12" s="49" t="n"/>
+      <c r="C12" s="62" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="62" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="62" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="62" t="n"/>
+      <c r="K12" s="49" t="n"/>
+      <c r="L12" s="62" t="n"/>
+      <c r="M12" s="56" t="n"/>
+      <c r="N12" s="49" t="n"/>
+      <c r="O12" s="62" t="n"/>
+      <c r="P12" s="49" t="n"/>
+      <c r="Q12" s="62" t="n"/>
+      <c r="R12" s="49" t="n"/>
+      <c r="S12" s="62" t="n"/>
+      <c r="T12" s="49" t="n"/>
     </row>
     <row r="13" ht="22.05" customHeight="1">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="26" t="n"/>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="26" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="26" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="28" t="n"/>
-      <c r="N13" s="26" t="n"/>
-      <c r="O13" s="27" t="n"/>
-      <c r="P13" s="26" t="n"/>
-      <c r="Q13" s="27" t="n"/>
-      <c r="R13" s="26" t="n"/>
-      <c r="S13" s="27" t="n"/>
-      <c r="T13" s="26" t="n"/>
+      <c r="B13" s="49" t="n"/>
+      <c r="C13" s="62" t="n"/>
+      <c r="D13" s="56" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="62" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="62" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="62" t="n"/>
+      <c r="K13" s="49" t="n"/>
+      <c r="L13" s="62" t="n"/>
+      <c r="M13" s="56" t="n"/>
+      <c r="N13" s="49" t="n"/>
+      <c r="O13" s="62" t="n"/>
+      <c r="P13" s="49" t="n"/>
+      <c r="Q13" s="62" t="n"/>
+      <c r="R13" s="49" t="n"/>
+      <c r="S13" s="62" t="n"/>
+      <c r="T13" s="49" t="n"/>
     </row>
     <row r="14" ht="22.05" customHeight="1">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="26" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="26" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="28" t="n"/>
-      <c r="N14" s="26" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="26" t="n"/>
-      <c r="Q14" s="27" t="n"/>
-      <c r="R14" s="26" t="n"/>
-      <c r="S14" s="27" t="n"/>
-      <c r="T14" s="26" t="n"/>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="62" t="n"/>
+      <c r="D14" s="56" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="62" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="62" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="62" t="n"/>
+      <c r="K14" s="49" t="n"/>
+      <c r="L14" s="62" t="n"/>
+      <c r="M14" s="56" t="n"/>
+      <c r="N14" s="49" t="n"/>
+      <c r="O14" s="62" t="n"/>
+      <c r="P14" s="49" t="n"/>
+      <c r="Q14" s="62" t="n"/>
+      <c r="R14" s="49" t="n"/>
+      <c r="S14" s="62" t="n"/>
+      <c r="T14" s="49" t="n"/>
     </row>
     <row r="15" ht="22.05" customHeight="1">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="26" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="26" t="n"/>
-      <c r="J15" s="27" t="n"/>
-      <c r="K15" s="26" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="28" t="n"/>
-      <c r="N15" s="26" t="n"/>
-      <c r="O15" s="27" t="n"/>
-      <c r="P15" s="26" t="n"/>
-      <c r="Q15" s="27" t="n"/>
-      <c r="R15" s="26" t="n"/>
-      <c r="S15" s="27" t="n"/>
-      <c r="T15" s="26" t="n"/>
+      <c r="B15" s="49" t="n"/>
+      <c r="C15" s="62" t="n"/>
+      <c r="D15" s="56" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="62" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="62" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="62" t="n"/>
+      <c r="K15" s="49" t="n"/>
+      <c r="L15" s="62" t="n"/>
+      <c r="M15" s="56" t="n"/>
+      <c r="N15" s="49" t="n"/>
+      <c r="O15" s="62" t="n"/>
+      <c r="P15" s="49" t="n"/>
+      <c r="Q15" s="62" t="n"/>
+      <c r="R15" s="49" t="n"/>
+      <c r="S15" s="62" t="n"/>
+      <c r="T15" s="49" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="26" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="28" t="n"/>
-      <c r="N16" s="26" t="n"/>
-      <c r="O16" s="27" t="n"/>
-      <c r="P16" s="26" t="n"/>
-      <c r="Q16" s="27" t="n"/>
-      <c r="R16" s="26" t="n"/>
-      <c r="S16" s="27" t="n"/>
-      <c r="T16" s="26" t="n"/>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="62" t="n"/>
+      <c r="D16" s="56" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="62" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="62" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="62" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="62" t="n"/>
+      <c r="M16" s="56" t="n"/>
+      <c r="N16" s="49" t="n"/>
+      <c r="O16" s="62" t="n"/>
+      <c r="P16" s="49" t="n"/>
+      <c r="Q16" s="62" t="n"/>
+      <c r="R16" s="49" t="n"/>
+      <c r="S16" s="62" t="n"/>
+      <c r="T16" s="49" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="61" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="26" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="26" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="26" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="28" t="n"/>
-      <c r="N17" s="26" t="n"/>
-      <c r="O17" s="27" t="n"/>
-      <c r="P17" s="26" t="n"/>
-      <c r="Q17" s="27" t="n"/>
-      <c r="R17" s="26" t="n"/>
-      <c r="S17" s="27" t="n"/>
-      <c r="T17" s="26" t="n"/>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="62" t="n"/>
+      <c r="D17" s="56" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="62" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="62" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="62" t="n"/>
+      <c r="K17" s="49" t="n"/>
+      <c r="L17" s="62" t="n"/>
+      <c r="M17" s="56" t="n"/>
+      <c r="N17" s="49" t="n"/>
+      <c r="O17" s="62" t="n"/>
+      <c r="P17" s="49" t="n"/>
+      <c r="Q17" s="62" t="n"/>
+      <c r="R17" s="49" t="n"/>
+      <c r="S17" s="62" t="n"/>
+      <c r="T17" s="49" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="28" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="27" t="n"/>
-      <c r="K18" s="26" t="n"/>
-      <c r="L18" s="27" t="n"/>
-      <c r="M18" s="28" t="n"/>
-      <c r="N18" s="26" t="n"/>
-      <c r="O18" s="27" t="n"/>
-      <c r="P18" s="26" t="n"/>
-      <c r="Q18" s="27" t="n"/>
-      <c r="R18" s="26" t="n"/>
-      <c r="S18" s="27" t="n"/>
-      <c r="T18" s="26" t="n"/>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="62" t="n"/>
+      <c r="D18" s="56" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="62" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="62" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="62" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="62" t="n"/>
+      <c r="M18" s="56" t="n"/>
+      <c r="N18" s="49" t="n"/>
+      <c r="O18" s="62" t="n"/>
+      <c r="P18" s="49" t="n"/>
+      <c r="Q18" s="62" t="n"/>
+      <c r="R18" s="49" t="n"/>
+      <c r="S18" s="62" t="n"/>
+      <c r="T18" s="49" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="61" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="26" t="n"/>
-      <c r="H19" s="27" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="27" t="n"/>
-      <c r="K19" s="26" t="n"/>
-      <c r="L19" s="27" t="n"/>
-      <c r="M19" s="28" t="n"/>
-      <c r="N19" s="26" t="n"/>
-      <c r="O19" s="27" t="n"/>
-      <c r="P19" s="26" t="n"/>
-      <c r="Q19" s="27" t="n"/>
-      <c r="R19" s="26" t="n"/>
-      <c r="S19" s="27" t="n"/>
-      <c r="T19" s="26" t="n"/>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="62" t="n"/>
+      <c r="D19" s="56" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="62" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="62" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="62" t="n"/>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="62" t="n"/>
+      <c r="M19" s="56" t="n"/>
+      <c r="N19" s="49" t="n"/>
+      <c r="O19" s="62" t="n"/>
+      <c r="P19" s="49" t="n"/>
+      <c r="Q19" s="62" t="n"/>
+      <c r="R19" s="49" t="n"/>
+      <c r="S19" s="62" t="n"/>
+      <c r="T19" s="49" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="61" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="26" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="26" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="28" t="n"/>
-      <c r="N20" s="26" t="n"/>
-      <c r="O20" s="27" t="n"/>
-      <c r="P20" s="26" t="n"/>
-      <c r="Q20" s="27" t="n"/>
-      <c r="R20" s="26" t="n"/>
-      <c r="S20" s="27" t="n"/>
-      <c r="T20" s="26" t="n"/>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="62" t="n"/>
+      <c r="D20" s="56" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="62" t="n"/>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="62" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="62" t="n"/>
+      <c r="K20" s="49" t="n"/>
+      <c r="L20" s="62" t="n"/>
+      <c r="M20" s="56" t="n"/>
+      <c r="N20" s="49" t="n"/>
+      <c r="O20" s="62" t="n"/>
+      <c r="P20" s="49" t="n"/>
+      <c r="Q20" s="62" t="n"/>
+      <c r="R20" s="49" t="n"/>
+      <c r="S20" s="62" t="n"/>
+      <c r="T20" s="49" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="28" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="27" t="n"/>
-      <c r="I21" s="26" t="n"/>
-      <c r="J21" s="27" t="n"/>
-      <c r="K21" s="26" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="28" t="n"/>
-      <c r="N21" s="26" t="n"/>
-      <c r="O21" s="27" t="n"/>
-      <c r="P21" s="26" t="n"/>
-      <c r="Q21" s="27" t="n"/>
-      <c r="R21" s="26" t="n"/>
-      <c r="S21" s="27" t="n"/>
-      <c r="T21" s="26" t="n"/>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="62" t="n"/>
+      <c r="D21" s="56" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="62" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="62" t="n"/>
+      <c r="K21" s="49" t="n"/>
+      <c r="L21" s="62" t="n"/>
+      <c r="M21" s="56" t="n"/>
+      <c r="N21" s="49" t="n"/>
+      <c r="O21" s="62" t="n"/>
+      <c r="P21" s="49" t="n"/>
+      <c r="Q21" s="62" t="n"/>
+      <c r="R21" s="49" t="n"/>
+      <c r="S21" s="62" t="n"/>
+      <c r="T21" s="49" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="61" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="26" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="27" t="n"/>
-      <c r="I22" s="26" t="n"/>
-      <c r="J22" s="27" t="n"/>
-      <c r="K22" s="26" t="n"/>
-      <c r="L22" s="27" t="n"/>
-      <c r="M22" s="28" t="n"/>
-      <c r="N22" s="26" t="n"/>
-      <c r="O22" s="27" t="n"/>
-      <c r="P22" s="26" t="n"/>
-      <c r="Q22" s="27" t="n"/>
-      <c r="R22" s="26" t="n"/>
-      <c r="S22" s="27" t="n"/>
-      <c r="T22" s="26" t="n"/>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="62" t="n"/>
+      <c r="D22" s="56" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="62" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="62" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="62" t="n"/>
+      <c r="K22" s="49" t="n"/>
+      <c r="L22" s="62" t="n"/>
+      <c r="M22" s="56" t="n"/>
+      <c r="N22" s="49" t="n"/>
+      <c r="O22" s="62" t="n"/>
+      <c r="P22" s="49" t="n"/>
+      <c r="Q22" s="62" t="n"/>
+      <c r="R22" s="49" t="n"/>
+      <c r="S22" s="62" t="n"/>
+      <c r="T22" s="49" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1">
-      <c r="A23" s="25" t="n">
+      <c r="A23" s="61" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="28" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="26" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="26" t="n"/>
-      <c r="J23" s="27" t="n"/>
-      <c r="K23" s="26" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="28" t="n"/>
-      <c r="N23" s="26" t="n"/>
-      <c r="O23" s="27" t="n"/>
-      <c r="P23" s="26" t="n"/>
-      <c r="Q23" s="27" t="n"/>
-      <c r="R23" s="26" t="n"/>
-      <c r="S23" s="27" t="n"/>
-      <c r="T23" s="26" t="n"/>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="62" t="n"/>
+      <c r="D23" s="56" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="62" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="62" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="62" t="n"/>
+      <c r="K23" s="49" t="n"/>
+      <c r="L23" s="62" t="n"/>
+      <c r="M23" s="56" t="n"/>
+      <c r="N23" s="49" t="n"/>
+      <c r="O23" s="62" t="n"/>
+      <c r="P23" s="49" t="n"/>
+      <c r="Q23" s="62" t="n"/>
+      <c r="R23" s="49" t="n"/>
+      <c r="S23" s="62" t="n"/>
+      <c r="T23" s="49" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>APPROVAL / الاعتماد</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="18" t="n"/>
-      <c r="P25" s="18" t="n"/>
-      <c r="Q25" s="18" t="n"/>
-      <c r="R25" s="18" t="n"/>
-      <c r="S25" s="18" t="n"/>
-      <c r="T25" s="7" t="n"/>
+      <c r="B25" s="56" t="n"/>
+      <c r="C25" s="56" t="n"/>
+      <c r="D25" s="56" t="n"/>
+      <c r="E25" s="56" t="n"/>
+      <c r="F25" s="56" t="n"/>
+      <c r="G25" s="56" t="n"/>
+      <c r="H25" s="56" t="n"/>
+      <c r="I25" s="56" t="n"/>
+      <c r="J25" s="56" t="n"/>
+      <c r="K25" s="56" t="n"/>
+      <c r="L25" s="56" t="n"/>
+      <c r="M25" s="56" t="n"/>
+      <c r="N25" s="56" t="n"/>
+      <c r="O25" s="56" t="n"/>
+      <c r="P25" s="56" t="n"/>
+      <c r="Q25" s="56" t="n"/>
+      <c r="R25" s="56" t="n"/>
+      <c r="S25" s="56" t="n"/>
+      <c r="T25" s="49" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="63" t="inlineStr">
         <is>
           <t>☐ Approved for organic sale / معتمد للبيع كعضوي   ☐ Hold (re-inspection) / حجز (إعادة فحص)   ☐ Rejected (not organic) / مرفوض (غير عضوي)</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n"/>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="28" t="n"/>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="28" t="n"/>
-      <c r="G26" s="28" t="n"/>
-      <c r="H26" s="28" t="n"/>
-      <c r="I26" s="28" t="n"/>
-      <c r="J26" s="28" t="n"/>
-      <c r="K26" s="28" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="28" t="n"/>
-      <c r="N26" s="28" t="n"/>
-      <c r="O26" s="28" t="n"/>
-      <c r="P26" s="28" t="n"/>
-      <c r="Q26" s="28" t="n"/>
-      <c r="R26" s="28" t="n"/>
-      <c r="S26" s="28" t="n"/>
-      <c r="T26" s="26" t="n"/>
+      <c r="B26" s="56" t="n"/>
+      <c r="C26" s="56" t="n"/>
+      <c r="D26" s="56" t="n"/>
+      <c r="E26" s="56" t="n"/>
+      <c r="F26" s="56" t="n"/>
+      <c r="G26" s="56" t="n"/>
+      <c r="H26" s="56" t="n"/>
+      <c r="I26" s="56" t="n"/>
+      <c r="J26" s="56" t="n"/>
+      <c r="K26" s="56" t="n"/>
+      <c r="L26" s="56" t="n"/>
+      <c r="M26" s="56" t="n"/>
+      <c r="N26" s="56" t="n"/>
+      <c r="O26" s="56" t="n"/>
+      <c r="P26" s="56" t="n"/>
+      <c r="Q26" s="56" t="n"/>
+      <c r="R26" s="56" t="n"/>
+      <c r="S26" s="56" t="n"/>
+      <c r="T26" s="49" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>NOTES / ملاحظات</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="18" t="n"/>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="18" t="n"/>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="18" t="n"/>
-      <c r="N28" s="18" t="n"/>
-      <c r="O28" s="18" t="n"/>
-      <c r="P28" s="18" t="n"/>
-      <c r="Q28" s="18" t="n"/>
-      <c r="R28" s="18" t="n"/>
-      <c r="S28" s="18" t="n"/>
-      <c r="T28" s="7" t="n"/>
+      <c r="B28" s="56" t="n"/>
+      <c r="C28" s="56" t="n"/>
+      <c r="D28" s="56" t="n"/>
+      <c r="E28" s="56" t="n"/>
+      <c r="F28" s="56" t="n"/>
+      <c r="G28" s="56" t="n"/>
+      <c r="H28" s="56" t="n"/>
+      <c r="I28" s="56" t="n"/>
+      <c r="J28" s="56" t="n"/>
+      <c r="K28" s="56" t="n"/>
+      <c r="L28" s="56" t="n"/>
+      <c r="M28" s="56" t="n"/>
+      <c r="N28" s="56" t="n"/>
+      <c r="O28" s="56" t="n"/>
+      <c r="P28" s="56" t="n"/>
+      <c r="Q28" s="56" t="n"/>
+      <c r="R28" s="56" t="n"/>
+      <c r="S28" s="56" t="n"/>
+      <c r="T28" s="49" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="64" t="inlineStr">
         <is>
           <t>Gaps found and corrective actions.</t>
         </is>
       </c>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="32" t="n"/>
+      <c r="B29" s="46" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
+      <c r="E29" s="46" t="n"/>
+      <c r="F29" s="46" t="n"/>
+      <c r="G29" s="46" t="n"/>
+      <c r="H29" s="46" t="n"/>
+      <c r="I29" s="46" t="n"/>
+      <c r="J29" s="46" t="n"/>
+      <c r="K29" s="46" t="n"/>
+      <c r="L29" s="46" t="n"/>
+      <c r="M29" s="46" t="n"/>
+      <c r="N29" s="46" t="n"/>
+      <c r="O29" s="46" t="n"/>
+      <c r="P29" s="46" t="n"/>
+      <c r="Q29" s="46" t="n"/>
+      <c r="R29" s="46" t="n"/>
+      <c r="S29" s="46" t="n"/>
+      <c r="T29" s="47" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="33" t="n"/>
-      <c r="B30" s="34" t="n"/>
-      <c r="C30" s="34" t="n"/>
-      <c r="D30" s="34" t="n"/>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="34" t="n"/>
-      <c r="G30" s="34" t="n"/>
-      <c r="H30" s="34" t="n"/>
-      <c r="I30" s="34" t="n"/>
-      <c r="J30" s="34" t="n"/>
-      <c r="K30" s="34" t="n"/>
-      <c r="L30" s="34" t="n"/>
-      <c r="M30" s="34" t="n"/>
-      <c r="N30" s="34" t="n"/>
-      <c r="O30" s="34" t="n"/>
-      <c r="P30" s="34" t="n"/>
-      <c r="Q30" s="34" t="n"/>
-      <c r="R30" s="34" t="n"/>
-      <c r="S30" s="34" t="n"/>
-      <c r="T30" s="35" t="n"/>
+      <c r="A30" s="65" t="n"/>
+      <c r="B30" s="53" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
+      <c r="E30" s="53" t="n"/>
+      <c r="F30" s="53" t="n"/>
+      <c r="G30" s="53" t="n"/>
+      <c r="H30" s="53" t="n"/>
+      <c r="I30" s="53" t="n"/>
+      <c r="J30" s="53" t="n"/>
+      <c r="K30" s="53" t="n"/>
+      <c r="L30" s="53" t="n"/>
+      <c r="M30" s="53" t="n"/>
+      <c r="N30" s="53" t="n"/>
+      <c r="O30" s="53" t="n"/>
+      <c r="P30" s="53" t="n"/>
+      <c r="Q30" s="53" t="n"/>
+      <c r="R30" s="53" t="n"/>
+      <c r="S30" s="53" t="n"/>
+      <c r="T30" s="54" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t>Area Supervisor / مسؤول المنطقة</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="37" t="inlineStr">
+      <c r="B32" s="56" t="n"/>
+      <c r="C32" s="56" t="n"/>
+      <c r="D32" s="56" t="n"/>
+      <c r="E32" s="56" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="67" t="inlineStr">
         <is>
           <t>OCS / GOTS Coordinator / منسق OCS / GOTS</t>
         </is>
       </c>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="18" t="n"/>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="37" t="inlineStr">
+      <c r="H32" s="56" t="n"/>
+      <c r="I32" s="56" t="n"/>
+      <c r="J32" s="56" t="n"/>
+      <c r="K32" s="56" t="n"/>
+      <c r="L32" s="49" t="n"/>
+      <c r="M32" s="67" t="inlineStr">
         <is>
           <t>Quality / الجودة</t>
         </is>
       </c>
-      <c r="N32" s="18" t="n"/>
-      <c r="O32" s="18" t="n"/>
-      <c r="P32" s="18" t="n"/>
-      <c r="Q32" s="18" t="n"/>
-      <c r="R32" s="18" t="n"/>
-      <c r="S32" s="18" t="n"/>
-      <c r="T32" s="7" t="n"/>
+      <c r="N32" s="56" t="n"/>
+      <c r="O32" s="56" t="n"/>
+      <c r="P32" s="56" t="n"/>
+      <c r="Q32" s="56" t="n"/>
+      <c r="R32" s="56" t="n"/>
+      <c r="S32" s="56" t="n"/>
+      <c r="T32" s="49" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n"/>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="39" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="32" t="n"/>
-      <c r="M33" s="39" t="n"/>
-      <c r="N33" s="31" t="n"/>
-      <c r="O33" s="31" t="n"/>
-      <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="31" t="n"/>
-      <c r="R33" s="31" t="n"/>
-      <c r="S33" s="31" t="n"/>
-      <c r="T33" s="32" t="n"/>
+      <c r="A33" s="68" t="n"/>
+      <c r="B33" s="46" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
+      <c r="E33" s="46" t="n"/>
+      <c r="F33" s="47" t="n"/>
+      <c r="G33" s="69" t="n"/>
+      <c r="H33" s="46" t="n"/>
+      <c r="I33" s="46" t="n"/>
+      <c r="J33" s="46" t="n"/>
+      <c r="K33" s="46" t="n"/>
+      <c r="L33" s="47" t="n"/>
+      <c r="M33" s="69" t="n"/>
+      <c r="N33" s="46" t="n"/>
+      <c r="O33" s="46" t="n"/>
+      <c r="P33" s="46" t="n"/>
+      <c r="Q33" s="46" t="n"/>
+      <c r="R33" s="46" t="n"/>
+      <c r="S33" s="46" t="n"/>
+      <c r="T33" s="47" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="n"/>
-      <c r="B34" s="41" t="n"/>
-      <c r="C34" s="41" t="n"/>
-      <c r="D34" s="41" t="n"/>
-      <c r="E34" s="41" t="n"/>
-      <c r="F34" s="42" t="n"/>
-      <c r="G34" s="43" t="n"/>
-      <c r="H34" s="41" t="n"/>
-      <c r="I34" s="41" t="n"/>
-      <c r="J34" s="41" t="n"/>
-      <c r="K34" s="41" t="n"/>
-      <c r="L34" s="42" t="n"/>
-      <c r="M34" s="43" t="n"/>
-      <c r="N34" s="41" t="n"/>
-      <c r="O34" s="41" t="n"/>
-      <c r="P34" s="41" t="n"/>
-      <c r="Q34" s="41" t="n"/>
-      <c r="R34" s="41" t="n"/>
-      <c r="S34" s="41" t="n"/>
-      <c r="T34" s="42" t="n"/>
+      <c r="A34" s="70" t="n"/>
+      <c r="F34" s="51" t="n"/>
+      <c r="G34" s="50" t="n"/>
+      <c r="L34" s="51" t="n"/>
+      <c r="M34" s="50" t="n"/>
+      <c r="T34" s="51" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="n"/>
-      <c r="B35" s="34" t="n"/>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="35" t="n"/>
-      <c r="G35" s="44" t="n"/>
-      <c r="H35" s="34" t="n"/>
-      <c r="I35" s="34" t="n"/>
-      <c r="J35" s="34" t="n"/>
-      <c r="K35" s="34" t="n"/>
-      <c r="L35" s="35" t="n"/>
-      <c r="M35" s="44" t="n"/>
-      <c r="N35" s="34" t="n"/>
-      <c r="O35" s="34" t="n"/>
-      <c r="P35" s="34" t="n"/>
-      <c r="Q35" s="34" t="n"/>
-      <c r="R35" s="34" t="n"/>
-      <c r="S35" s="34" t="n"/>
-      <c r="T35" s="35" t="n"/>
+      <c r="A35" s="65" t="n"/>
+      <c r="B35" s="53" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+      <c r="E35" s="53" t="n"/>
+      <c r="F35" s="54" t="n"/>
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="53" t="n"/>
+      <c r="I35" s="53" t="n"/>
+      <c r="J35" s="53" t="n"/>
+      <c r="K35" s="53" t="n"/>
+      <c r="L35" s="54" t="n"/>
+      <c r="M35" s="52" t="n"/>
+      <c r="N35" s="53" t="n"/>
+      <c r="O35" s="53" t="n"/>
+      <c r="P35" s="53" t="n"/>
+      <c r="Q35" s="53" t="n"/>
+      <c r="R35" s="53" t="n"/>
+      <c r="S35" s="53" t="n"/>
+      <c r="T35" s="54" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="55" t="inlineStr">
         <is>
           <t>Retention: at least 5 years or per certification body / customer requirement. Any nonconformity opens a corrective action (DÖF). | الاحتفاظ: 5 سنوات على الأقل أو حسب متطلبات جهة الاعتماد / العميل. وتفتح أي حالة عدم مطابقة إجراءً تصحيحيًا (DÖF).</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n"/>
-      <c r="C36" s="18" t="n"/>
-      <c r="D36" s="18" t="n"/>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n"/>
-      <c r="G36" s="18" t="n"/>
-      <c r="H36" s="18" t="n"/>
-      <c r="I36" s="18" t="n"/>
-      <c r="J36" s="18" t="n"/>
-      <c r="K36" s="18" t="n"/>
-      <c r="L36" s="18" t="n"/>
-      <c r="M36" s="18" t="n"/>
-      <c r="N36" s="18" t="n"/>
-      <c r="O36" s="18" t="n"/>
-      <c r="P36" s="18" t="n"/>
-      <c r="Q36" s="18" t="n"/>
-      <c r="R36" s="18" t="n"/>
-      <c r="S36" s="18" t="n"/>
-      <c r="T36" s="7" t="n"/>
+      <c r="B36" s="56" t="n"/>
+      <c r="C36" s="56" t="n"/>
+      <c r="D36" s="56" t="n"/>
+      <c r="E36" s="56" t="n"/>
+      <c r="F36" s="56" t="n"/>
+      <c r="G36" s="56" t="n"/>
+      <c r="H36" s="56" t="n"/>
+      <c r="I36" s="56" t="n"/>
+      <c r="J36" s="56" t="n"/>
+      <c r="K36" s="56" t="n"/>
+      <c r="L36" s="56" t="n"/>
+      <c r="M36" s="56" t="n"/>
+      <c r="N36" s="56" t="n"/>
+      <c r="O36" s="56" t="n"/>
+      <c r="P36" s="56" t="n"/>
+      <c r="Q36" s="56" t="n"/>
+      <c r="R36" s="56" t="n"/>
+      <c r="S36" s="56" t="n"/>
+      <c r="T36" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="143">
@@ -1641,8 +1755,8 @@
     <mergeCell ref="K7:O7"/>
     <mergeCell ref="M33:T35"/>
     <mergeCell ref="M32:T32"/>
+    <mergeCell ref="L12:N12"/>
     <mergeCell ref="H14:I14"/>
-    <mergeCell ref="L12:N12"/>
     <mergeCell ref="A10:T10"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="C16:E16"/>
